--- a/data/24August-89ers-v-Razorbacks.xlsx
+++ b/data/24August-89ers-v-Razorbacks.xlsx
@@ -214,7 +214,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O129"/>
   <sheetData>
     <row r="1">
@@ -459,8 +459,10 @@
       <c r="D24" t="s">
         <v>18</v>
       </c>
-      <c r="E24" t="s">
-        <v>19</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DCLC</t>
+        </is>
       </c>
       <c r="L24" t="s">
         <v>20</v>
@@ -509,8 +511,10 @@
       <c r="D28" t="s">
         <v>18</v>
       </c>
-      <c r="E28" t="s">
-        <v>23</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="L28" t="s">
         <v>24</v>
@@ -598,8 +602,10 @@
       <c r="D35" t="s">
         <v>18</v>
       </c>
-      <c r="E35" t="s">
-        <v>23</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -639,8 +645,10 @@
       <c r="D39" t="s">
         <v>29</v>
       </c>
-      <c r="E39" t="s">
-        <v>30</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
       </c>
       <c r="L39" t="s">
         <v>31</v>
@@ -719,8 +727,10 @@
       <c r="D46" t="s">
         <v>18</v>
       </c>
-      <c r="E46" t="s">
-        <v>36</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DCUC</t>
+        </is>
       </c>
       <c r="L46">
         <v>69</v>
